--- a/approval_forms/024_public_safety_equipment_requisition_form--approval_forms.xlsx
+++ b/approval_forms/024_public_safety_equipment_requisition_form--approval_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +970,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'safety_and_security'}</t>
+          <t>safety_and_security</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Safety and Security'}</t>
+          <t>Safety and Security</t>
         </is>
       </c>
     </row>
@@ -987,12 +987,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'departmental_manager'}</t>
+          <t>departmental_manager</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Departmental Manager'}</t>
+          <t>Departmental Manager</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'departmental_director'}</t>
+          <t>departmental_director</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Departmental Director'}</t>
+          <t>Departmental Director</t>
         </is>
       </c>
     </row>
@@ -1089,12 +1089,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'both'}</t>
+          <t>both</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Both'}</t>
+          <t>Both</t>
         </is>
       </c>
     </row>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1123,12 +1123,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'John'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
